--- a/donation_forms/037_wrestling_pins_pledge_form--donation_forms.xlsx
+++ b/donation_forms/037_wrestling_pins_pledge_form--donation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>banjo</t>
+          <t>kazoo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Banjo</t>
+          <t>Kazoo</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kazoo</t>
+          <t>dulcimer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazoo</t>
+          <t>Dulcimer</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>dulcimer</t>
+          <t>sitar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dulcimer</t>
+          <t>Sitar</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sitar</t>
+          <t>lute</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sitar</t>
+          <t>Lute</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>lute</t>
+          <t>harpsichord</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lute</t>
+          <t>Harpsichord</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>harpsichord</t>
+          <t>lyre</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Harpsichord</t>
+          <t>Lyre</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>harp</t>
+          <t>koto</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Harp</t>
+          <t>Koto</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>lyre</t>
+          <t>shamisen</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lyre</t>
+          <t>Shamisen</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>lute</t>
+          <t>guqin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lute</t>
+          <t>Guqin</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>koto</t>
+          <t>guzhur</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Koto</t>
+          <t>Guzhur</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>shamisen</t>
+          <t>kora</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shamisen</t>
+          <t>Kora</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>guqin</t>
+          <t>bouzouki</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Guqin</t>
+          <t>Bouzouki</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>guzhur</t>
+          <t>balalaika</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Guzhur</t>
+          <t>Balalaika</t>
         </is>
       </c>
     </row>
@@ -1563,469 +1563,129 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>guqin</t>
+          <t>saz</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Guqin</t>
+          <t>Saz</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>additional_instrument_choices</t>
+          <t>required_fields_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>koto</t>
+          <t>pledge_amount</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Koto</t>
+          <t>Pledge Amount</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>additional_instrument_choices</t>
+          <t>required_fields_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kora</t>
+          <t>pin_amount</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kora</t>
+          <t>Pin Amount</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>additional_instrument_choices</t>
+          <t>required_fields_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>bouzouki</t>
+          <t>pledge_frequency</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bouzouki</t>
+          <t>Pledge Frequency</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>additional_instrument_choices</t>
+          <t>required_fields_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>balalaika</t>
+          <t>pledge_start_date</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Balalaika</t>
+          <t>Pledge Start Date</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>additional_instrument_choices</t>
+          <t>required_fields_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>saz</t>
+          <t>pledge_end_date</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saz</t>
+          <t>Pledge End Date</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>additional_instrument_choices</t>
+          <t>required_fields_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>saz</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saz</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>additional_instrument_choices</t>
+          <t>required_fields_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>sitar</t>
+          <t>additional_instrument</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
-        <is>
-          <t>Sitar</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>sitar</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Sitar</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>sitar</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Sitar</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>sitar</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Sitar</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>additional_instrument_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>banjo</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Banjo</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>required_fields_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>pledge_amount</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Pledge Amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>required_fields_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>pin_amount</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Pin Amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>required_fields_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>pledge_frequency</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Pledge Frequency</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>required_fields_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>pledge_start_date</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Pledge Start Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>required_fields_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>pledge_end_date</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Pledge End Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>required_fields_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>required_fields_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>additional_instrument</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
         <is>
           <t>Additional Instrument</t>
         </is>
